--- a/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_pet/sub-0001_ses-01_pet_pdf.xlsx
+++ b/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_pet/sub-0001_ses-01_pet_pdf.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -243,7 +244,7 @@
         <v>0</v>
       </c>
       <c r="V1" s="0">
-        <v>0.030637254901960786</v>
+        <v>0.030637254901960787</v>
       </c>
       <c r="W1" s="0">
         <v>0.017094017094017096</v>
@@ -701,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="BB2" s="0">
-        <v>0.1576976148235758</v>
+        <v>0.15769761482357581</v>
       </c>
       <c r="BC2" s="0">
         <v>0.021161334010496021</v>
@@ -812,7 +813,7 @@
         <v>0.0031577617784514338</v>
       </c>
       <c r="CM2" s="0">
-        <v>0.018632383081796162</v>
+        <v>0.018632383081796163</v>
       </c>
       <c r="CN2" s="0">
         <v>0.023929169657812877</v>
@@ -1078,7 +1079,7 @@
         <v>0</v>
       </c>
       <c r="BG3" s="0">
-        <v>0.018484288354898334</v>
+        <v>0.018484288354898335</v>
       </c>
       <c r="BH3" s="0">
         <v>0.016733601070950468</v>
@@ -2101,7 +2102,7 @@
         <v>0.052002080083203332</v>
       </c>
       <c r="AL6" s="0">
-        <v>0.070935706455149294</v>
+        <v>0.070935706455149295</v>
       </c>
       <c r="AM6" s="0">
         <v>0</v>
@@ -2149,7 +2150,7 @@
         <v>0.041941910454021181</v>
       </c>
       <c r="BB6" s="0">
-        <v>0.42381233983835997</v>
+        <v>0.42381233983835998</v>
       </c>
       <c r="BC6" s="0">
         <v>0.055019468427289657</v>
@@ -2463,7 +2464,7 @@
         <v>0.014857737166629524</v>
       </c>
       <c r="AL7" s="0">
-        <v>0.0967305088024763</v>
+        <v>0.096730508802476301</v>
       </c>
       <c r="AM7" s="0">
         <v>0</v>
@@ -2511,16 +2512,16 @@
         <v>0.083883820908042361</v>
       </c>
       <c r="BB7" s="0">
-        <v>0.42381233983835997</v>
+        <v>0.42381233983835998</v>
       </c>
       <c r="BC7" s="0">
-        <v>0.084645336041984084</v>
+        <v>0.084645336041984085</v>
       </c>
       <c r="BD7" s="0">
         <v>0.020554984583761562</v>
       </c>
       <c r="BE7" s="0">
-        <v>0.062509767151117362</v>
+        <v>0.062509767151117363</v>
       </c>
       <c r="BF7" s="0">
         <v>0</v>
@@ -2568,7 +2569,7 @@
         <v>0.059357245823793779</v>
       </c>
       <c r="BU7" s="0">
-        <v>0.20723241114910373</v>
+        <v>0.20723241114910374</v>
       </c>
       <c r="BV7" s="0">
         <v>0</v>
@@ -2894,7 +2895,7 @@
         <v>0.055778670236501564</v>
       </c>
       <c r="BI8" s="0">
-        <v>0.046620046620046623</v>
+        <v>0.046620046620046624</v>
       </c>
       <c r="BJ8" s="0">
         <v>0.07002026902524415</v>
@@ -3235,7 +3236,7 @@
         <v>0.12582573136206343</v>
       </c>
       <c r="BB9" s="0">
-        <v>0.70963926670609045</v>
+        <v>0.70963926670609046</v>
       </c>
       <c r="BC9" s="0">
         <v>0.12696800406297601</v>
@@ -3271,7 +3272,7 @@
         <v>0.0057940784518222327</v>
       </c>
       <c r="BN9" s="0">
-        <v>0.031046258925799416</v>
+        <v>0.031046258925799417</v>
       </c>
       <c r="BO9" s="0">
         <v>0.090059664527749564</v>
@@ -3444,7 +3445,7 @@
         <v>0.037631710988459646</v>
       </c>
       <c r="C10" s="0">
-        <v>0.035351303579319523</v>
+        <v>0.035351303579319524</v>
       </c>
       <c r="D10" s="0">
         <v>0.019124115509657695</v>
@@ -3624,7 +3625,7 @@
         <v>0.16215220195319713</v>
       </c>
       <c r="BK10" s="0">
-        <v>0.020605810838656521</v>
+        <v>0.020605810838656522</v>
       </c>
       <c r="BL10" s="0">
         <v>0.070054770092981847</v>
@@ -3711,10 +3712,10 @@
         <v>0.093161915408980889</v>
       </c>
       <c r="CN10" s="0">
-        <v>0.19143335726250318</v>
+        <v>0.19143335726250319</v>
       </c>
       <c r="CO10" s="0">
-        <v>0.09697610861324174</v>
+        <v>0.096976108613241741</v>
       </c>
       <c r="CP10" s="0">
         <v>0.53963304952632263</v>
@@ -3878,7 +3879,7 @@
         <v>0.068634179821551081</v>
       </c>
       <c r="AA11" s="0">
-        <v>0.23453532688361164</v>
+        <v>0.23453532688361165</v>
       </c>
       <c r="AB11" s="0">
         <v>0.12262415695892079</v>
@@ -3917,7 +3918,7 @@
         <v>0</v>
       </c>
       <c r="AN11" s="0">
-        <v>0.21729682746631881</v>
+        <v>0.21729682746631882</v>
       </c>
       <c r="AO11" s="0">
         <v>0.044943820224719058</v>
@@ -3941,7 +3942,7 @@
         <v>0.030909990108803138</v>
       </c>
       <c r="AV11" s="0">
-        <v>0.0074521201281764603</v>
+        <v>0.0074521201281764604</v>
       </c>
       <c r="AW11" s="0">
         <v>0</v>
@@ -4001,7 +4002,7 @@
         <v>0.18011932905549913</v>
       </c>
       <c r="BP11" s="0">
-        <v>0.02204585537918869</v>
+        <v>0.022045855379188691</v>
       </c>
       <c r="BQ11" s="0">
         <v>0.023929169657812853</v>
@@ -4037,10 +4038,10 @@
         <v>0.2005012531328319</v>
       </c>
       <c r="CB11" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC11" s="0">
-        <v>0.074990626171728469</v>
+        <v>0.07499062617172847</v>
       </c>
       <c r="CD11" s="0">
         <v>0.025641025641025619</v>
@@ -4061,7 +4062,7 @@
         <v>0.055463117027176878</v>
       </c>
       <c r="CJ11" s="0">
-        <v>0.031625553447185296</v>
+        <v>0.031625553447185297</v>
       </c>
       <c r="CK11" s="0">
         <v>0.031218958422023529</v>
@@ -4079,7 +4080,7 @@
         <v>0.15428017279379339</v>
       </c>
       <c r="CP11" s="0">
-        <v>0.57161130431306661</v>
+        <v>0.57161130431306662</v>
       </c>
       <c r="CQ11" s="0">
         <v>0</v>
@@ -4216,7 +4217,7 @@
         <v>0.045913682277318686</v>
       </c>
       <c r="S12" s="0">
-        <v>0.037150552614470179</v>
+        <v>0.03715055261447018</v>
       </c>
       <c r="T12" s="0">
         <v>0.020487604998975638</v>
@@ -4228,7 +4229,7 @@
         <v>0.15318627450980407</v>
       </c>
       <c r="W12" s="0">
-        <v>0.068376068376068438</v>
+        <v>0.068376068376068439</v>
       </c>
       <c r="X12" s="0">
         <v>0.037900322152738336</v>
@@ -4324,7 +4325,7 @@
         <v>0.7884880741178798</v>
       </c>
       <c r="BC12" s="0">
-        <v>0.24123920771965487</v>
+        <v>0.24123920771965488</v>
       </c>
       <c r="BD12" s="0">
         <v>0.17129153819801318</v>
@@ -4384,7 +4385,7 @@
         <v>0</v>
       </c>
       <c r="BW12" s="0">
-        <v>0.087719298245614113</v>
+        <v>0.087719298245614114</v>
       </c>
       <c r="BX12" s="0">
         <v>0.084139671855279846</v>
@@ -4533,7 +4534,7 @@
         <v>0.11783767859773152</v>
       </c>
       <c r="D13" s="0">
-        <v>0.024588148512416991</v>
+        <v>0.024588148512416992</v>
       </c>
       <c r="E13" s="0">
         <v>0.046724605177086216</v>
@@ -4596,7 +4597,7 @@
         <v>0.09475080538184566</v>
       </c>
       <c r="Y13" s="0">
-        <v>0.68134171907756746</v>
+        <v>0.68134171907756747</v>
       </c>
       <c r="Z13" s="0">
         <v>0.022878059940517025</v>
@@ -4635,7 +4636,7 @@
         <v>0.10400416016640657</v>
       </c>
       <c r="AL13" s="0">
-        <v>0.19346101760495243</v>
+        <v>0.19346101760495244</v>
       </c>
       <c r="AM13" s="0">
         <v>0</v>
@@ -4713,7 +4714,7 @@
         <v>0.089291846967511412</v>
       </c>
       <c r="BL13" s="0">
-        <v>0.16558400203795678</v>
+        <v>0.16558400203795679</v>
       </c>
       <c r="BM13" s="0">
         <v>0.017382235355466697</v>
@@ -4785,7 +4786,7 @@
         <v>0.088740987243483005</v>
       </c>
       <c r="CJ13" s="0">
-        <v>0.031625553447185296</v>
+        <v>0.031625553447185297</v>
       </c>
       <c r="CK13" s="0">
         <v>0.11636157230026951</v>
@@ -4797,7 +4798,7 @@
         <v>0.093161915408980722</v>
       </c>
       <c r="CN13" s="0">
-        <v>0.40679588418281853</v>
+        <v>0.40679588418281854</v>
       </c>
       <c r="CO13" s="0">
         <v>0.29974433571365572</v>
@@ -4943,7 +4944,7 @@
         <v>0.083588743382557895</v>
       </c>
       <c r="T14" s="0">
-        <v>0.081950419995902551</v>
+        <v>0.081950419995902552</v>
       </c>
       <c r="U14" s="0">
         <v>0</v>
@@ -5012,7 +5013,7 @@
         <v>0.20603384841795458</v>
       </c>
       <c r="AQ14" s="0">
-        <v>0.12875536480686708</v>
+        <v>0.12875536480686709</v>
       </c>
       <c r="AR14" s="0">
         <v>0.074766355140186994</v>
@@ -5069,7 +5070,7 @@
         <v>0.15061861215707384</v>
       </c>
       <c r="BJ14" s="0">
-        <v>0.28376635341809497</v>
+        <v>0.28376635341809498</v>
       </c>
       <c r="BK14" s="0">
         <v>0.04808022529019855</v>
@@ -5087,7 +5088,7 @@
         <v>0.16886187098953073</v>
       </c>
       <c r="BP14" s="0">
-        <v>0.088183421516754928</v>
+        <v>0.088183421516754929</v>
       </c>
       <c r="BQ14" s="0">
         <v>0.047858339315625796</v>
@@ -5365,10 +5366,10 @@
         <v>0</v>
       </c>
       <c r="AN15" s="0">
-        <v>0.21729682746631881</v>
+        <v>0.21729682746631882</v>
       </c>
       <c r="AO15" s="0">
-        <v>0.089887640449438116</v>
+        <v>0.089887640449438117</v>
       </c>
       <c r="AP15" s="0">
         <v>0.27961736571008072</v>
@@ -5401,16 +5402,16 @@
         <v>0.040444893832153654</v>
       </c>
       <c r="AZ15" s="0">
-        <v>0.57428677287884355</v>
+        <v>0.57428677287884356</v>
       </c>
       <c r="BA15" s="0">
-        <v>0.32504980601866384</v>
+        <v>0.32504980601866385</v>
       </c>
       <c r="BB15" s="0">
         <v>0.94618568894145394</v>
       </c>
       <c r="BC15" s="0">
-        <v>0.36397494498053123</v>
+        <v>0.36397494498053124</v>
       </c>
       <c r="BD15" s="0">
         <v>0.17129153819801285</v>
@@ -5422,7 +5423,7 @@
         <v>0.041649312786338995</v>
       </c>
       <c r="BG15" s="0">
-        <v>0.30807147258163869</v>
+        <v>0.3080714725816387</v>
       </c>
       <c r="BH15" s="0">
         <v>0.37929495760821025</v>
@@ -5497,7 +5498,7 @@
         <v>0.063492063492063433</v>
       </c>
       <c r="CF15" s="0">
-        <v>0.80598733448474313</v>
+        <v>0.80598733448474314</v>
       </c>
       <c r="CG15" s="0">
         <v>0.059091177687171252</v>
@@ -5616,7 +5617,7 @@
         <v>0.091988626860679129</v>
       </c>
       <c r="C16" s="0">
-        <v>0.18559434379142747</v>
+        <v>0.18559434379142748</v>
       </c>
       <c r="D16" s="0">
         <v>0.079228478540010458</v>
@@ -5661,7 +5662,7 @@
         <v>0.10288065843621408</v>
       </c>
       <c r="R16" s="0">
-        <v>0.18365472910927474</v>
+        <v>0.18365472910927475</v>
       </c>
       <c r="S16" s="0">
         <v>0.10680783876660176</v>
@@ -5727,7 +5728,7 @@
         <v>0.061785603954278713</v>
       </c>
       <c r="AN16" s="0">
-        <v>0.34767492394611071</v>
+        <v>0.34767492394611072</v>
       </c>
       <c r="AO16" s="0">
         <v>0.10486891385767801</v>
@@ -5820,7 +5821,7 @@
         <v>0.064583837894566939</v>
       </c>
       <c r="BS16" s="0">
-        <v>1.0137727694979612</v>
+        <v>1.0137727694979613</v>
       </c>
       <c r="BT16" s="0">
         <v>0.34342406512337859</v>
@@ -5972,7 +5973,7 @@
     </row>
     <row r="17">
       <c r="A17" s="0">
-        <v>0.24554200378376181</v>
+        <v>0.24554200378376182</v>
       </c>
       <c r="B17" s="0">
         <v>0.15888944639571823</v>
@@ -6005,7 +6006,7 @@
         <v>0.11402508551881405</v>
       </c>
       <c r="L17" s="0">
-        <v>0.23086485526549438</v>
+        <v>0.23086485526549439</v>
       </c>
       <c r="M17" s="0">
         <v>0.12474012474012464</v>
@@ -6089,7 +6090,7 @@
         <v>0.030892801977139301</v>
       </c>
       <c r="AN17" s="0">
-        <v>0.21729682746631881</v>
+        <v>0.21729682746631882</v>
       </c>
       <c r="AO17" s="0">
         <v>0.14981273408239687</v>
@@ -6101,7 +6102,7 @@
         <v>0.30042918454935597</v>
       </c>
       <c r="AR17" s="0">
-        <v>0.2367601246105917</v>
+        <v>0.23676012461059171</v>
       </c>
       <c r="AS17" s="0">
         <v>0.39682539682539647</v>
@@ -6134,7 +6135,7 @@
         <v>1.2320126158091849</v>
       </c>
       <c r="BC17" s="0">
-        <v>0.37243947858472964</v>
+        <v>0.37243947858472965</v>
       </c>
       <c r="BD17" s="0">
         <v>0.32887975334018471</v>
@@ -6155,7 +6156,7 @@
         <v>0.19723865877712013</v>
       </c>
       <c r="BJ17" s="0">
-        <v>0.49382716049382674</v>
+        <v>0.49382716049382675</v>
       </c>
       <c r="BK17" s="0">
         <v>0.10302905419328243</v>
@@ -6185,7 +6186,7 @@
         <v>1.0905125408942193</v>
       </c>
       <c r="BT17" s="0">
-        <v>0.39006190112778732</v>
+        <v>0.39006190112778733</v>
       </c>
       <c r="BU17" s="0">
         <v>0.9843539529582418</v>
@@ -6376,7 +6377,7 @@
         <v>0.22845275181723759</v>
       </c>
       <c r="O18" s="0">
-        <v>0.20433722233208076</v>
+        <v>0.20433722233208077</v>
       </c>
       <c r="P18" s="0">
         <v>0.17061934823408959</v>
@@ -6493,7 +6494,7 @@
         <v>0.60815770158330651</v>
       </c>
       <c r="BB18" s="0">
-        <v>1.1038833037650297</v>
+        <v>1.1038833037650298</v>
       </c>
       <c r="BC18" s="0">
         <v>0.62637548671068166</v>
@@ -6795,13 +6796,13 @@
         <v>0.55832201599517284</v>
       </c>
       <c r="AH19" s="0">
-        <v>0.20615287028227144</v>
+        <v>0.20615287028227145</v>
       </c>
       <c r="AI19" s="0">
         <v>0.35471774602209488</v>
       </c>
       <c r="AJ19" s="0">
-        <v>0.89783281733746378</v>
+        <v>0.89783281733746379</v>
       </c>
       <c r="AK19" s="0">
         <v>0.23772379466607305</v>
@@ -6837,7 +6838,7 @@
         <v>0.1730959446092982</v>
       </c>
       <c r="AV19" s="0">
-        <v>0.08197332140994136</v>
+        <v>0.081973321409941361</v>
       </c>
       <c r="AW19" s="0">
         <v>0.0089702188733405339</v>
@@ -6873,7 +6874,7 @@
         <v>0.67159581022797477</v>
       </c>
       <c r="BH19" s="0">
-        <v>0.56894243641231756</v>
+        <v>0.56894243641231757</v>
       </c>
       <c r="BI19" s="0">
         <v>0.28689259458490307</v>
@@ -6915,7 +6916,7 @@
         <v>1.1915863641073496</v>
       </c>
       <c r="BV19" s="0">
-        <v>0.081900081900082133</v>
+        <v>0.081900081900082134</v>
       </c>
       <c r="BW19" s="0">
         <v>0.24853801169590711</v>
@@ -7002,7 +7003,7 @@
         <v>0.047938638542665522</v>
       </c>
       <c r="CY19" s="0">
-        <v>0.040521922359996874</v>
+        <v>0.040521922359996875</v>
       </c>
       <c r="CZ19" s="0">
         <v>0.0077681970014759801</v>
@@ -7070,7 +7071,7 @@
         <v>0.19124115509657663</v>
       </c>
       <c r="E20" s="0">
-        <v>0.2429679469208483</v>
+        <v>0.24296794692084831</v>
       </c>
       <c r="F20" s="0">
         <v>0.18076956184901422</v>
@@ -7465,7 +7466,7 @@
         <v>0.34275921165381285</v>
       </c>
       <c r="P21" s="0">
-        <v>0.30711482682136126</v>
+        <v>0.30711482682136127</v>
       </c>
       <c r="Q21" s="0">
         <v>0.36008230452674861</v>
@@ -7486,7 +7487,7 @@
         <v>0.73529411764705821</v>
       </c>
       <c r="W21" s="0">
-        <v>0.66666666666666607</v>
+        <v>0.66666666666666608</v>
       </c>
       <c r="X21" s="0">
         <v>0.4737540269092283</v>
@@ -7507,7 +7508,7 @@
         <v>0.023640661938534261</v>
       </c>
       <c r="AD21" s="0">
-        <v>0.071377587437544548</v>
+        <v>0.071377587437544549</v>
       </c>
       <c r="AE21" s="0">
         <v>0.20491803278688506</v>
@@ -7516,7 +7517,7 @@
         <v>0.56140350877192935</v>
       </c>
       <c r="AG21" s="0">
-        <v>0.746944318696242</v>
+        <v>0.74694431869624201</v>
       </c>
       <c r="AH21" s="0">
         <v>0.37266095781795083</v>
@@ -7585,7 +7586,7 @@
         <v>0.7533434907736577</v>
       </c>
       <c r="BD21" s="0">
-        <v>0.76053442959917716</v>
+        <v>0.76053442959917717</v>
       </c>
       <c r="BE21" s="0">
         <v>0.70323488045006965</v>
@@ -7633,7 +7634,7 @@
         <v>1.2197584716668677</v>
       </c>
       <c r="BT21" s="0">
-        <v>0.62325108114983407</v>
+        <v>0.62325108114983408</v>
       </c>
       <c r="BU21" s="0">
         <v>1.0776085379753384</v>
@@ -7669,7 +7670,7 @@
         <v>0.57142857142857095</v>
       </c>
       <c r="CF21" s="0">
-        <v>1.4968336211859516</v>
+        <v>1.4968336211859517</v>
       </c>
       <c r="CG21" s="0">
         <v>0.17727353306151378</v>
@@ -7690,7 +7691,7 @@
         <v>0.41998231653404033</v>
       </c>
       <c r="CM21" s="0">
-        <v>0.80119247251723424</v>
+        <v>0.80119247251723425</v>
       </c>
       <c r="CN21" s="0">
         <v>0.95716678631251406</v>
@@ -7726,7 +7727,7 @@
         <v>0.1917545541706614</v>
       </c>
       <c r="CY21" s="0">
-        <v>0.24313153415998034</v>
+        <v>0.24313153415998035</v>
       </c>
       <c r="CZ21" s="0">
         <v>0.031072788005903802</v>
@@ -7806,7 +7807,7 @@
         <v>0.20183671409829429</v>
       </c>
       <c r="I22" s="0">
-        <v>0.17718715393133982</v>
+        <v>0.17718715393133983</v>
       </c>
       <c r="J22" s="0">
         <v>0.39005051473879371</v>
@@ -7845,7 +7846,7 @@
         <v>0.1673173452314555</v>
       </c>
       <c r="V22" s="0">
-        <v>0.68933823529411697</v>
+        <v>0.68933823529411698</v>
       </c>
       <c r="W22" s="0">
         <v>0.44444444444444409</v>
@@ -7929,7 +7930,7 @@
         <v>0.035880875493362004</v>
       </c>
       <c r="AX22" s="0">
-        <v>0.31398764306694998</v>
+        <v>0.31398764306694999</v>
       </c>
       <c r="AY22" s="0">
         <v>0.18200202224469145</v>
@@ -7944,7 +7945,7 @@
         <v>1.4488468361916014</v>
       </c>
       <c r="BC22" s="0">
-        <v>0.86338242762823691</v>
+        <v>0.86338242762823692</v>
       </c>
       <c r="BD22" s="0">
         <v>0.6988694758478925</v>
@@ -7980,7 +7981,7 @@
         <v>0.25871882438166177</v>
       </c>
       <c r="BO22" s="0">
-        <v>0.66419002589215292</v>
+        <v>0.66419002589215293</v>
       </c>
       <c r="BP22" s="0">
         <v>0.2425044091710756</v>
@@ -8159,7 +8160,7 @@
         <v>0.36133694670280136</v>
       </c>
       <c r="F23" s="0">
-        <v>0.30415196120627896</v>
+        <v>0.30415196120627897</v>
       </c>
       <c r="G23" s="0">
         <v>0.44070512820512941</v>
@@ -8177,7 +8178,7 @@
         <v>0.60813378943367713</v>
       </c>
       <c r="L23" s="0">
-        <v>0.42621204049014499</v>
+        <v>0.426212040490145</v>
       </c>
       <c r="M23" s="0">
         <v>0.47124047124047258</v>
@@ -8231,10 +8232,10 @@
         <v>0.023640661938534348</v>
       </c>
       <c r="AD23" s="0">
-        <v>0.14275517487508962</v>
+        <v>0.14275517487508963</v>
       </c>
       <c r="AE23" s="0">
-        <v>0.54644808743169559</v>
+        <v>0.5464480874316956</v>
       </c>
       <c r="AF23" s="0">
         <v>0.49122807017543996</v>
@@ -8249,10 +8250,10 @@
         <v>0.54727880814837493</v>
       </c>
       <c r="AJ23" s="0">
-        <v>1.1558307533539764</v>
+        <v>1.1558307533539765</v>
       </c>
       <c r="AK23" s="0">
-        <v>0.69831364683158947</v>
+        <v>0.69831364683158948</v>
       </c>
       <c r="AL23" s="0">
         <v>0.86412587863545742</v>
@@ -8276,7 +8277,7 @@
         <v>0.54828660436137222</v>
       </c>
       <c r="AS23" s="0">
-        <v>0.72751322751322955</v>
+        <v>0.72751322751322956</v>
       </c>
       <c r="AT23" s="0">
         <v>0.16694490818030097</v>
@@ -8366,7 +8367,7 @@
         <v>0.21294021294021354</v>
       </c>
       <c r="BW23" s="0">
-        <v>0.38011695906432857</v>
+        <v>0.38011695906432858</v>
       </c>
       <c r="BX23" s="0">
         <v>0.57495442434441324</v>
@@ -8432,13 +8433,13 @@
         <v>0.10653030787259006</v>
       </c>
       <c r="CS23" s="0">
-        <v>0.029485478401887154</v>
+        <v>0.029485478401887155</v>
       </c>
       <c r="CT23" s="0">
         <v>0.013349352556401052</v>
       </c>
       <c r="CU23" s="0">
-        <v>0.29940119760479122</v>
+        <v>0.29940119760479123</v>
       </c>
       <c r="CV23" s="0">
         <v>0</v>
@@ -8465,7 +8466,7 @@
         <v>0</v>
       </c>
       <c r="DD23" s="0">
-        <v>0.006071645415907728</v>
+        <v>0.0060716454159077281</v>
       </c>
       <c r="DE23" s="0">
         <v>0</v>
@@ -8489,7 +8490,7 @@
         <v>0</v>
       </c>
       <c r="DL23" s="0">
-        <v>0.17406440382941737</v>
+        <v>0.17406440382941738</v>
       </c>
       <c r="DM23" s="0">
         <v>0.14245014245014287</v>
@@ -8602,7 +8603,7 @@
         <v>0.70175438596491169</v>
       </c>
       <c r="AG24" s="0">
-        <v>1.1468236004225127</v>
+        <v>1.1468236004225128</v>
       </c>
       <c r="AH24" s="0">
         <v>0.5946717411988578</v>
@@ -8644,7 +8645,7 @@
         <v>0.11129660545353358</v>
       </c>
       <c r="AU24" s="0">
-        <v>0.49455984174085021</v>
+        <v>0.49455984174085022</v>
       </c>
       <c r="AV24" s="0">
         <v>0.275728444742529</v>
@@ -8692,7 +8693,7 @@
         <v>1.0097659848903622</v>
       </c>
       <c r="BK24" s="0">
-        <v>0.37777319870870218</v>
+        <v>0.37777319870870219</v>
       </c>
       <c r="BL24" s="0">
         <v>0.79607693287479231</v>
@@ -8737,7 +8738,7 @@
         <v>1.1148272017837224</v>
       </c>
       <c r="BZ24" s="0">
-        <v>1.0926803580832007</v>
+        <v>1.0926803580832008</v>
       </c>
       <c r="CA24" s="0">
         <v>0.75187969924811959</v>
@@ -9012,7 +9013,7 @@
         <v>0.32789328563976422</v>
       </c>
       <c r="AW25" s="0">
-        <v>0.14352350197344801</v>
+        <v>0.14352350197344802</v>
       </c>
       <c r="AX25" s="0">
         <v>0.62797528613389997</v>
@@ -9039,7 +9040,7 @@
         <v>0.92201906547898027</v>
       </c>
       <c r="BF25" s="0">
-        <v>0.2637789809801469</v>
+        <v>0.26377898098014691</v>
       </c>
       <c r="BG25" s="0">
         <v>1.0474430067775715</v>
@@ -9069,7 +9070,7 @@
         <v>1.1370032646628381</v>
       </c>
       <c r="BP25" s="0">
-        <v>0.4850088183421512</v>
+        <v>0.48500881834215121</v>
       </c>
       <c r="BQ25" s="0">
         <v>0.46661880832735059</v>
@@ -9090,10 +9091,10 @@
         <v>0.19656019656019638</v>
       </c>
       <c r="BW25" s="0">
-        <v>0.80409356725146119</v>
+        <v>0.8040935672514612</v>
       </c>
       <c r="BX25" s="0">
-        <v>0.77128032534006385</v>
+        <v>0.77128032534006386</v>
       </c>
       <c r="BY25" s="0">
         <v>1.1984392419175016</v>
@@ -9114,7 +9115,7 @@
         <v>0.2948717948717946</v>
       </c>
       <c r="CE25" s="0">
-        <v>0.82539682539682468</v>
+        <v>0.82539682539682469</v>
       </c>
       <c r="CF25" s="0">
         <v>1.2089810017271145</v>
@@ -9242,7 +9243,7 @@
         <v>0.50269103625385847</v>
       </c>
       <c r="E26" s="0">
-        <v>0.60430489362364836</v>
+        <v>0.60430489362364837</v>
       </c>
       <c r="F26" s="0">
         <v>0.51074574617657986</v>
@@ -9299,7 +9300,7 @@
         <v>0.87179487179487103</v>
       </c>
       <c r="X26" s="0">
-        <v>0.79590676520750347</v>
+        <v>0.79590676520750348</v>
       </c>
       <c r="Y26" s="0">
         <v>1.3888888888888875</v>
@@ -9377,7 +9378,7 @@
         <v>0.17043415859346953</v>
       </c>
       <c r="AX26" s="0">
-        <v>0.76977615719639358</v>
+        <v>0.76977615719639359</v>
       </c>
       <c r="AY26" s="0">
         <v>0.46511627906976705</v>
@@ -9392,7 +9393,7 @@
         <v>1.2320126158091849</v>
       </c>
       <c r="BC26" s="0">
-        <v>1.0834603013373953</v>
+        <v>1.0834603013373954</v>
       </c>
       <c r="BD26" s="0">
         <v>1.000342583076395</v>
@@ -9422,7 +9423,7 @@
         <v>0.88523754935676913</v>
       </c>
       <c r="BM26" s="0">
-        <v>0.35343878556115615</v>
+        <v>0.35343878556115616</v>
       </c>
       <c r="BN26" s="0">
         <v>0.50708889578805705</v>
@@ -9509,7 +9510,7 @@
         <v>1.1857533280437265</v>
       </c>
       <c r="CP26" s="0">
-        <v>1.2791301914697994</v>
+        <v>1.2791301914697995</v>
       </c>
       <c r="CQ26" s="0">
         <v>0.097529258777633215</v>
@@ -9533,7 +9534,7 @@
         <v>0.12134449702705971</v>
       </c>
       <c r="CX26" s="0">
-        <v>2.8763183125599205</v>
+        <v>2.8763183125599206</v>
       </c>
       <c r="CY26" s="0">
         <v>2.7554907204797767</v>
@@ -9637,7 +9638,7 @@
         <v>0.78439127282314869</v>
       </c>
       <c r="P27" s="0">
-        <v>0.64835352328954043</v>
+        <v>0.64835352328954044</v>
       </c>
       <c r="Q27" s="0">
         <v>0.82304526748971119</v>
@@ -9700,7 +9701,7 @@
         <v>1.3828689370485023</v>
       </c>
       <c r="AK27" s="0">
-        <v>0.84689101849788206</v>
+        <v>0.84689101849788207</v>
       </c>
       <c r="AL27" s="0">
         <v>1.1736635068033781</v>
@@ -9766,7 +9767,7 @@
         <v>0.49979175343606785</v>
       </c>
       <c r="BG27" s="0">
-        <v>1.2014787430683906</v>
+        <v>1.2014787430683907</v>
       </c>
       <c r="BH27" s="0">
         <v>1.215975011155733</v>
@@ -9814,13 +9815,13 @@
         <v>0.31122031122031096</v>
       </c>
       <c r="BW27" s="0">
-        <v>0.73099415204678297</v>
+        <v>0.73099415204678298</v>
       </c>
       <c r="BX27" s="0">
         <v>0.96760622633571647</v>
       </c>
       <c r="BY27" s="0">
-        <v>1.282051282051281</v>
+        <v>1.2820512820512811</v>
       </c>
       <c r="BZ27" s="0">
         <v>1.355976829910478</v>
@@ -9853,7 +9854,7 @@
         <v>0.74320576816417017</v>
       </c>
       <c r="CJ27" s="0">
-        <v>0.81172253847775599</v>
+        <v>0.811722538477756</v>
       </c>
       <c r="CK27" s="0">
         <v>0.92237831701433148</v>
@@ -9889,7 +9890,7 @@
         <v>1.6966067864271441</v>
       </c>
       <c r="CV27" s="0">
-        <v>0.87064676616915337</v>
+        <v>0.87064676616915338</v>
       </c>
       <c r="CW27" s="0">
         <v>0.15774784613517762</v>
@@ -9993,7 +9994,7 @@
         <v>0.79002079002079229</v>
       </c>
       <c r="N28" s="0">
-        <v>0.82035306334371993</v>
+        <v>0.82035306334371994</v>
       </c>
       <c r="O28" s="0">
         <v>0.79757431942522139</v>
@@ -10116,7 +10117,7 @@
         <v>1.0644589000591396</v>
       </c>
       <c r="BC28" s="0">
-        <v>1.2866091078381618</v>
+        <v>1.2866091078381619</v>
       </c>
       <c r="BD28" s="0">
         <v>0.95238095238095499</v>
@@ -10140,7 +10141,7 @@
         <v>1.1719181868435631</v>
       </c>
       <c r="BK28" s="0">
-        <v>0.85170684799780449</v>
+        <v>0.8517068479978045</v>
       </c>
       <c r="BL28" s="0">
         <v>1.2227741688956855</v>
@@ -10200,7 +10201,7 @@
         <v>0.39743589743589858</v>
       </c>
       <c r="CE28" s="0">
-        <v>1.3968253968254007</v>
+        <v>1.3968253968254008</v>
       </c>
       <c r="CF28" s="0">
         <v>0.63327576280944331</v>
@@ -10224,7 +10225,7 @@
         <v>1.0294303397751703</v>
       </c>
       <c r="CM28" s="0">
-        <v>0.93161915408981077</v>
+        <v>0.93161915408981078</v>
       </c>
       <c r="CN28" s="0">
         <v>1.2921751615218988</v>
@@ -10233,7 +10234,7 @@
         <v>1.2827294366569726</v>
       </c>
       <c r="CP28" s="0">
-        <v>1.1752008634128825</v>
+        <v>1.1752008634128826</v>
       </c>
       <c r="CQ28" s="0">
         <v>0.39553532726484725</v>
@@ -10245,7 +10246,7 @@
         <v>1.0025062656641632</v>
       </c>
       <c r="CT28" s="0">
-        <v>0.18689093578961471</v>
+        <v>0.18689093578961472</v>
       </c>
       <c r="CU28" s="0">
         <v>1.9960079840319418</v>
@@ -10254,7 +10255,7 @@
         <v>1.4925373134328399</v>
       </c>
       <c r="CW28" s="0">
-        <v>0.27909234316223835</v>
+        <v>0.27909234316223836</v>
       </c>
       <c r="CX28" s="0">
         <v>3.8830297219559071</v>
@@ -10275,7 +10276,7 @@
         <v>0.19458164945367512</v>
       </c>
       <c r="DD28" s="0">
-        <v>0.56466302367941867</v>
+        <v>0.56466302367941868</v>
       </c>
       <c r="DE28" s="0">
         <v>0.080554212985339352</v>
@@ -10382,7 +10383,7 @@
         <v>1.2867647058823519</v>
       </c>
       <c r="W29" s="0">
-        <v>0.85470085470085388</v>
+        <v>0.85470085470085389</v>
       </c>
       <c r="X29" s="0">
         <v>1.0233086981239332</v>
@@ -10496,19 +10497,19 @@
         <v>1.2550200803212841</v>
       </c>
       <c r="BI29" s="0">
-        <v>1.043571812802581</v>
+        <v>1.0435718128025811</v>
       </c>
       <c r="BJ29" s="0">
         <v>1.3193292795282832</v>
       </c>
       <c r="BK29" s="0">
-        <v>0.89291846967511423</v>
+        <v>0.89291846967511424</v>
       </c>
       <c r="BL29" s="0">
         <v>1.2928289389886627</v>
       </c>
       <c r="BM29" s="0">
-        <v>0.57940784518222332</v>
+        <v>0.57940784518222333</v>
       </c>
       <c r="BN29" s="0">
         <v>0.77615647314498526</v>
@@ -10532,7 +10533,7 @@
         <v>1.1532264902908496</v>
       </c>
       <c r="BU29" s="0">
-        <v>1.2744793285669866</v>
+        <v>1.2744793285669867</v>
       </c>
       <c r="BV29" s="0">
         <v>0.44226044226044187</v>
@@ -10595,7 +10596,7 @@
         <v>1.2871374415939334</v>
       </c>
       <c r="CP29" s="0">
-        <v>1.1791981452612212</v>
+        <v>1.1791981452612213</v>
       </c>
       <c r="CQ29" s="0">
         <v>0.62310359774599</v>
@@ -10640,7 +10641,7 @@
         <v>0.9168184578020635</v>
       </c>
       <c r="DE29" s="0">
-        <v>0.19333011116481374</v>
+        <v>0.19333011116481375</v>
       </c>
       <c r="DF29" s="0">
         <v>0.3578732106339465</v>
@@ -10813,7 +10814,7 @@
         <v>1.0582010582010573</v>
       </c>
       <c r="AT30" s="0">
-        <v>0.44518642181413431</v>
+        <v>0.44518642181413432</v>
       </c>
       <c r="AU30" s="0">
         <v>0.69238377843719023</v>
@@ -10885,7 +10886,7 @@
         <v>0.88537927733907562</v>
       </c>
       <c r="BR30" s="0">
-        <v>0.80729797368208533</v>
+        <v>0.80729797368208534</v>
       </c>
       <c r="BS30" s="0">
         <v>1.2197584716668677</v>
@@ -10948,7 +10949,7 @@
         <v>1.0925855753441951</v>
       </c>
       <c r="CM30" s="0">
-        <v>1.3787963480529148</v>
+        <v>1.3787963480529149</v>
       </c>
       <c r="CN30" s="0">
         <v>1.2682459918640812</v>
@@ -10975,7 +10976,7 @@
         <v>3.6926147704590786</v>
       </c>
       <c r="CV30" s="0">
-        <v>1.7412935323383067</v>
+        <v>1.7412935323383068</v>
       </c>
       <c r="CW30" s="0">
         <v>1.1042349229462434</v>
@@ -11049,7 +11050,7 @@
         <v>1.1430254823979957</v>
       </c>
       <c r="D31" s="0">
-        <v>0.95074174248012377</v>
+        <v>0.95074174248012378</v>
       </c>
       <c r="E31" s="0">
         <v>1.0684359717160381</v>
@@ -11058,7 +11059,7 @@
         <v>0.90671716736965857</v>
       </c>
       <c r="G31" s="0">
-        <v>1.028311965811965</v>
+        <v>1.0283119658119651</v>
       </c>
       <c r="H31" s="0">
         <v>0.73670400645877421</v>
@@ -11256,7 +11257,7 @@
         <v>1.2761807852115652</v>
       </c>
       <c r="BU31" s="0">
-        <v>1.1397782613200695</v>
+        <v>1.1397782613200696</v>
       </c>
       <c r="BV31" s="0">
         <v>0.47502047502047456</v>
@@ -11322,7 +11323,7 @@
         <v>0.95135307990566331</v>
       </c>
       <c r="CQ31" s="0">
-        <v>1.6309059384481996</v>
+        <v>1.6309059384481997</v>
       </c>
       <c r="CR31" s="0">
         <v>3.9895600298284828</v>
@@ -11376,7 +11377,7 @@
         <v>0.089126559714794926</v>
       </c>
       <c r="DI31" s="0">
-        <v>2.4922118380062281</v>
+        <v>2.4922118380062282</v>
       </c>
       <c r="DJ31" s="0">
         <v>1.5582655826558252</v>
@@ -11444,7 +11445,7 @@
         <v>1.0488058151609583</v>
       </c>
       <c r="O32" s="0">
-        <v>1.1007843912728263</v>
+        <v>1.1007843912728264</v>
       </c>
       <c r="P32" s="0">
         <v>1.0578399590513594</v>
@@ -11480,7 +11481,7 @@
         <v>1.1667810569663726</v>
       </c>
       <c r="AA32" s="0">
-        <v>1.3485781295807719</v>
+        <v>1.348578129580772</v>
       </c>
       <c r="AB32" s="0">
         <v>1.1649294911097519</v>
@@ -11507,7 +11508,7 @@
         <v>1.1452315800141921</v>
       </c>
       <c r="AJ32" s="0">
-        <v>1.1558307533539764</v>
+        <v>1.1558307533539765</v>
       </c>
       <c r="AK32" s="0">
         <v>1.3520540821632905</v>
@@ -11525,7 +11526,7 @@
         <v>0.85393258426966534</v>
       </c>
       <c r="AP32" s="0">
-        <v>1.3686534216335577</v>
+        <v>1.3686534216335578</v>
       </c>
       <c r="AQ32" s="0">
         <v>1.0443490701001459</v>
@@ -11588,7 +11589,7 @@
         <v>1.3746084392850599</v>
       </c>
       <c r="BK32" s="0">
-        <v>1.0715021636101409</v>
+        <v>1.071502163610141</v>
       </c>
       <c r="BL32" s="0">
         <v>1.3883581709336428</v>
@@ -11675,7 +11676,7 @@
         <v>1.3042668157257351</v>
       </c>
       <c r="CN32" s="0">
-        <v>1.244316822206273</v>
+        <v>1.2443168222062731</v>
       </c>
       <c r="CO32" s="0">
         <v>1.4281935995768356</v>
@@ -11705,7 +11706,7 @@
         <v>2.1113942482708468</v>
       </c>
       <c r="CX32" s="0">
-        <v>2.7484819431128233</v>
+        <v>2.7484819431128234</v>
       </c>
       <c r="CY32" s="0">
         <v>2.9337871788637733</v>
@@ -11875,7 +11876,7 @@
         <v>1.2554787905801936</v>
       </c>
       <c r="AL33" s="0">
-        <v>1.3671245244083305</v>
+        <v>1.3671245244083306</v>
       </c>
       <c r="AM33" s="0">
         <v>1.0812480691998754</v>
@@ -11941,7 +11942,7 @@
         <v>1.3308687615526791</v>
       </c>
       <c r="BH33" s="0">
-        <v>1.3498438197233364</v>
+        <v>1.3498438197233365</v>
       </c>
       <c r="BI33" s="0">
         <v>1.2730858884705027</v>
@@ -11992,7 +11993,7 @@
         <v>1.4303744215397549</v>
       </c>
       <c r="BY33" s="0">
-        <v>1.3238573021181705</v>
+        <v>1.3238573021181706</v>
       </c>
       <c r="BZ33" s="0">
         <v>1.3033175355450226</v>
@@ -12031,7 +12032,7 @@
         <v>1.1834823329076192</v>
       </c>
       <c r="CL33" s="0">
-        <v>1.3104711380573439</v>
+        <v>1.310471138057344</v>
       </c>
       <c r="CM33" s="0">
         <v>1.5278554127072839</v>
@@ -12118,7 +12119,7 @@
         <v>3.1901041666666639</v>
       </c>
       <c r="DO33" s="0">
-        <v>2.9126213592232983</v>
+        <v>2.9126213592232984</v>
       </c>
       <c r="DP33" s="0">
         <v>2.5821596244131428</v>
@@ -12141,7 +12142,7 @@
         <v>1.1930349188549345</v>
       </c>
       <c r="F34" s="0">
-        <v>1.1649593985825359</v>
+        <v>1.164959398582536</v>
       </c>
       <c r="G34" s="0">
         <v>1.1485042735042725</v>
@@ -12168,7 +12169,7 @@
         <v>1.0488058151609543</v>
       </c>
       <c r="O34" s="0">
-        <v>1.2392063805945543</v>
+        <v>1.2392063805945544</v>
       </c>
       <c r="P34" s="0">
         <v>1.268270488540066</v>
@@ -12177,7 +12178,7 @@
         <v>1.3888888888888875</v>
       </c>
       <c r="R34" s="0">
-        <v>1.377410468319558</v>
+        <v>1.3774104683195581</v>
       </c>
       <c r="S34" s="0">
         <v>1.1702424073558082</v>
@@ -12213,7 +12214,7 @@
         <v>0.37825059101654818</v>
       </c>
       <c r="AD34" s="0">
-        <v>0.54722817035450821</v>
+        <v>0.54722817035450822</v>
       </c>
       <c r="AE34" s="0">
         <v>1.092896174863387</v>
@@ -12288,7 +12289,7 @@
         <v>0.51251724817662092</v>
       </c>
       <c r="BC34" s="0">
-        <v>1.2696800406297601</v>
+        <v>1.2696800406297602</v>
       </c>
       <c r="BD34" s="0">
         <v>1.2744090441932157</v>
@@ -12327,7 +12328,7 @@
         <v>1.4859844647078675</v>
       </c>
       <c r="BP34" s="0">
-        <v>1.1537330981775415</v>
+        <v>1.1537330981775416</v>
       </c>
       <c r="BQ34" s="0">
         <v>1.0887772194304848</v>
@@ -12345,7 +12346,7 @@
         <v>1.0568852968604281</v>
       </c>
       <c r="BV34" s="0">
-        <v>0.76986076986076923</v>
+        <v>0.76986076986076924</v>
       </c>
       <c r="BW34" s="0">
         <v>1.286549707602338</v>
@@ -12369,7 +12370,7 @@
         <v>1.3748281464816887</v>
       </c>
       <c r="CD34" s="0">
-        <v>0.8846153846153838</v>
+        <v>0.88461538461538381</v>
       </c>
       <c r="CE34" s="0">
         <v>1.0793650793650784</v>
@@ -12393,7 +12394,7 @@
         <v>1.4190435646374331</v>
       </c>
       <c r="CL34" s="0">
-        <v>1.282051282051281</v>
+        <v>1.2820512820512811</v>
       </c>
       <c r="CM34" s="0">
         <v>1.2111049003167493</v>
@@ -12459,7 +12460,7 @@
         <v>2.7439024390243878</v>
       </c>
       <c r="DH34" s="0">
-        <v>1.158645276292334</v>
+        <v>1.1586452762923341</v>
       </c>
       <c r="DI34" s="0">
         <v>4.3613707165108995</v>
@@ -12605,7 +12606,7 @@
         <v>1.0194624652455968</v>
       </c>
       <c r="AN35" s="0">
-        <v>1.260321599304649</v>
+        <v>1.2603215993046491</v>
       </c>
       <c r="AO35" s="0">
         <v>1.1835205992509352</v>
@@ -12707,10 +12708,10 @@
         <v>0.71495181846440725</v>
       </c>
       <c r="BV35" s="0">
-        <v>0.93366093366093283</v>
+        <v>0.93366093366093284</v>
       </c>
       <c r="BW35" s="0">
-        <v>1.5204678362573087</v>
+        <v>1.5204678362573088</v>
       </c>
       <c r="BX35" s="0">
         <v>1.2200252419015554</v>
@@ -12734,7 +12735,7 @@
         <v>1.0897435897435888</v>
       </c>
       <c r="CE35" s="0">
-        <v>1.3333333333333321</v>
+        <v>1.3333333333333322</v>
       </c>
       <c r="CF35" s="0">
         <v>0.3454231433506042</v>
@@ -12800,7 +12801,7 @@
         <v>2.1362541754058864</v>
       </c>
       <c r="DA35" s="0">
-        <v>0.60038424591738659</v>
+        <v>0.6003842459173866</v>
       </c>
       <c r="DB35" s="0">
         <v>2.1421107628004163</v>
@@ -12815,7 +12816,7 @@
         <v>2.6582890285161893</v>
       </c>
       <c r="DF35" s="0">
-        <v>4.2603953646898391</v>
+        <v>4.2603953646898392</v>
       </c>
       <c r="DG35" s="0">
         <v>2.2357723577235755</v>
@@ -12839,13 +12840,13 @@
         <v>1.7094017094017078</v>
       </c>
       <c r="DN35" s="0">
-        <v>1.3020833333333321</v>
+        <v>1.3020833333333322</v>
       </c>
       <c r="DO35" s="0">
         <v>3.8025889967637507</v>
       </c>
       <c r="DP35" s="0">
-        <v>2.9342723004694808</v>
+        <v>2.9342723004694809</v>
       </c>
     </row>
     <row r="36">
@@ -12958,7 +12959,7 @@
         <v>1.1455108359133117</v>
       </c>
       <c r="AK36" s="0">
-        <v>1.2034767104969903</v>
+        <v>1.2034767104969904</v>
       </c>
       <c r="AL36" s="0">
         <v>1.0769329980009019</v>
@@ -12985,7 +12986,7 @@
         <v>1.719576719576718</v>
       </c>
       <c r="AT36" s="0">
-        <v>0.44518642181413431</v>
+        <v>0.44518642181413432</v>
       </c>
       <c r="AU36" s="0">
         <v>1.2611275964391682</v>
@@ -13024,7 +13025,7 @@
         <v>1.1939469665417177</v>
       </c>
       <c r="BG36" s="0">
-        <v>1.2076401725200236</v>
+        <v>1.2076401725200237</v>
       </c>
       <c r="BH36" s="0">
         <v>1.1936635430611324</v>
@@ -13099,7 +13100,7 @@
         <v>1.0793650793650784</v>
       </c>
       <c r="CF36" s="0">
-        <v>0.80598733448474313</v>
+        <v>0.80598733448474314</v>
       </c>
       <c r="CG36" s="0">
         <v>1.2704603202741818</v>
@@ -13350,7 +13351,7 @@
         <v>0.77907623817473504</v>
       </c>
       <c r="AU37" s="0">
-        <v>1.2796735905044498</v>
+        <v>1.2796735905044499</v>
       </c>
       <c r="AV37" s="0">
         <v>1.2221477010209394</v>
@@ -13371,7 +13372,7 @@
         <v>1.1219461046450656</v>
       </c>
       <c r="BB37" s="0">
-        <v>0.43366844076483307</v>
+        <v>0.43366844076483308</v>
       </c>
       <c r="BC37" s="0">
         <v>1.1088539021499904</v>
@@ -13470,10 +13471,10 @@
         <v>1.2234441941610343</v>
       </c>
       <c r="CI37" s="0">
-        <v>1.3422074320576804</v>
+        <v>1.3422074320576805</v>
       </c>
       <c r="CJ37" s="0">
-        <v>1.3388150959308442</v>
+        <v>1.3388150959308443</v>
       </c>
       <c r="CK37" s="0">
         <v>1.3339009507591872</v>
@@ -13580,7 +13581,7 @@
         <v>1.4090985114567747</v>
       </c>
       <c r="C38" s="0">
-        <v>1.3345117101193193</v>
+        <v>1.3345117101193194</v>
       </c>
       <c r="D38" s="0">
         <v>1.234871458623618</v>
@@ -13595,7 +13596,7 @@
         <v>1.4556623931624026</v>
       </c>
       <c r="H38" s="0">
-        <v>1.2009284488848599</v>
+        <v>1.20092844888486</v>
       </c>
       <c r="I38" s="0">
         <v>1.2735326688815145</v>
@@ -13646,7 +13647,7 @@
         <v>1.2317604699640026</v>
       </c>
       <c r="Y38" s="0">
-        <v>0.44549266247379748</v>
+        <v>0.44549266247379749</v>
       </c>
       <c r="Z38" s="0">
         <v>1.4870738961336176</v>
@@ -13694,7 +13695,7 @@
         <v>0.99956540634507385</v>
       </c>
       <c r="AO38" s="0">
-        <v>1.408239700374541</v>
+        <v>1.4082397003745411</v>
       </c>
       <c r="AP38" s="0">
         <v>1.2509197939661596</v>
@@ -13712,7 +13713,7 @@
         <v>0.61213132999443909</v>
       </c>
       <c r="AU38" s="0">
-        <v>1.2487636003956561</v>
+        <v>1.2487636003956562</v>
       </c>
       <c r="AV38" s="0">
         <v>1.2892167821745371</v>
@@ -13721,7 +13722,7 @@
         <v>0.92393254395407853</v>
       </c>
       <c r="AX38" s="0">
-        <v>1.2255646713258463</v>
+        <v>1.2255646713258464</v>
       </c>
       <c r="AY38" s="0">
         <v>1.3346814964610805</v>
@@ -13730,13 +13731,13 @@
         <v>0.76571569717179699</v>
       </c>
       <c r="BA38" s="0">
-        <v>0.83883820908042916</v>
+        <v>0.83883820908042917</v>
       </c>
       <c r="BB38" s="0">
         <v>0.32525133057362721</v>
       </c>
       <c r="BC38" s="0">
-        <v>1.0834603013374033</v>
+        <v>1.0834603013374034</v>
       </c>
       <c r="BD38" s="0">
         <v>1.1853374443302578</v>
@@ -13760,7 +13761,7 @@
         <v>0.95448682513359751</v>
       </c>
       <c r="BK38" s="0">
-        <v>1.3119032900611391</v>
+        <v>1.3119032900611392</v>
       </c>
       <c r="BL38" s="0">
         <v>1.139982167876711</v>
@@ -13811,7 +13812,7 @@
         <v>1.5037593984962503</v>
       </c>
       <c r="CB38" s="0">
-        <v>1.522309711286099</v>
+        <v>1.5223097112860991</v>
       </c>
       <c r="CC38" s="0">
         <v>1.5123109611298686</v>
@@ -13820,10 +13821,10 @@
         <v>1.1282051282051355</v>
       </c>
       <c r="CE38" s="0">
-        <v>1.1428571428571503</v>
+        <v>1.1428571428571504</v>
       </c>
       <c r="CF38" s="0">
-        <v>0.40299366724237456</v>
+        <v>0.40299366724237457</v>
       </c>
       <c r="CG38" s="0">
         <v>1.4418247355669893</v>
@@ -13928,7 +13929,7 @@
         <v>0.065104166666667088</v>
       </c>
       <c r="DO38" s="0">
-        <v>1.7799352750809176</v>
+        <v>1.7799352750809177</v>
       </c>
       <c r="DP38" s="0">
         <v>4.3427230046948635</v>
@@ -13942,7 +13943,7 @@
         <v>1.2460277638401061</v>
       </c>
       <c r="C39" s="0">
-        <v>1.216674031521578</v>
+        <v>1.2166740315215781</v>
       </c>
       <c r="D39" s="0">
         <v>1.30863590416086</v>
@@ -14002,10 +14003,10 @@
         <v>0.82720588235294035</v>
       </c>
       <c r="W39" s="0">
-        <v>1.3333333333333321</v>
+        <v>1.3333333333333322</v>
       </c>
       <c r="X39" s="0">
-        <v>1.3644115974985775</v>
+        <v>1.3644115974985776</v>
       </c>
       <c r="Y39" s="0">
         <v>0.34067085953878373</v>
@@ -14155,7 +14156,7 @@
         <v>0.41446482229820708</v>
       </c>
       <c r="BV39" s="0">
-        <v>1.3104013104013092</v>
+        <v>1.3104013104013093</v>
       </c>
       <c r="BW39" s="0">
         <v>1.1988304093567241</v>
@@ -14218,7 +14219,7 @@
         <v>0.4237118759243711</v>
       </c>
       <c r="CQ39" s="0">
-        <v>2.0101863892501068</v>
+        <v>2.0101863892501069</v>
       </c>
       <c r="CR39" s="0">
         <v>0.31959092361776897</v>
@@ -14227,13 +14228,13 @@
         <v>1.2457614624797275</v>
       </c>
       <c r="CT39" s="0">
-        <v>2.8834601521826166</v>
+        <v>2.8834601521826167</v>
       </c>
       <c r="CU39" s="0">
         <v>0</v>
       </c>
       <c r="CV39" s="0">
-        <v>0.87064676616915337</v>
+        <v>0.87064676616915338</v>
       </c>
       <c r="CW39" s="0">
         <v>2.4632932896493123</v>
@@ -14349,7 +14350,7 @@
         <v>1.4403292181069944</v>
       </c>
       <c r="R40" s="0">
-        <v>1.377410468319558</v>
+        <v>1.3774104683195581</v>
       </c>
       <c r="S40" s="0">
         <v>1.3652828085817765</v>
@@ -14364,7 +14365,7 @@
         <v>1.1335784313725479</v>
       </c>
       <c r="W40" s="0">
-        <v>1.3333333333333321</v>
+        <v>1.3333333333333322</v>
       </c>
       <c r="X40" s="0">
         <v>1.269660792116732</v>
@@ -14391,7 +14392,7 @@
         <v>1.2978142076502721</v>
       </c>
       <c r="AF40" s="0">
-        <v>1.3333333333333321</v>
+        <v>1.3333333333333322</v>
       </c>
       <c r="AG40" s="0">
         <v>0.9883808661536132</v>
@@ -14400,7 +14401,7 @@
         <v>1.1814145258483975</v>
       </c>
       <c r="AI40" s="0">
-        <v>1.1655011655011644</v>
+        <v>1.1655011655011645</v>
       </c>
       <c r="AJ40" s="0">
         <v>0.75335397316821395</v>
@@ -14427,7 +14428,7 @@
         <v>1.173104434907009</v>
       </c>
       <c r="AR40" s="0">
-        <v>1.3084112149532698</v>
+        <v>1.3084112149532699</v>
       </c>
       <c r="AS40" s="0">
         <v>0.92592592592592504</v>
@@ -14442,7 +14443,7 @@
         <v>1.5127803860198215</v>
       </c>
       <c r="AW40" s="0">
-        <v>1.1930391101542865</v>
+        <v>1.1930391101542866</v>
       </c>
       <c r="AX40" s="0">
         <v>1.2053074040311951</v>
@@ -14669,7 +14670,7 @@
         <v>1.266755044925614</v>
       </c>
       <c r="D41" s="0">
-        <v>1.2867797721498226</v>
+        <v>1.2867797721498227</v>
       </c>
       <c r="E41" s="0">
         <v>1.2117247609257691</v>
@@ -14816,7 +14817,7 @@
         <v>0.6483882919599846</v>
       </c>
       <c r="BA41" s="0">
-        <v>0.80738177623990703</v>
+        <v>0.80738177623990704</v>
       </c>
       <c r="BB41" s="0">
         <v>0.29568302779420436</v>
@@ -14921,7 +14922,7 @@
         <v>0.9095951192457008</v>
       </c>
       <c r="CJ41" s="0">
-        <v>1.3598987982289676</v>
+        <v>1.3598987982289677</v>
       </c>
       <c r="CK41" s="0">
         <v>1.1380729388392212</v>
@@ -15049,7 +15050,7 @@
         <v>1.4230343300110728</v>
       </c>
       <c r="J42" s="0">
-        <v>1.208517168616918</v>
+        <v>1.2085171686169181</v>
       </c>
       <c r="K42" s="0">
         <v>1.4633219308247802</v>
@@ -15145,7 +15146,7 @@
         <v>1.0187265917602988</v>
       </c>
       <c r="AP42" s="0">
-        <v>1.0448859455481962</v>
+        <v>1.0448859455481963</v>
       </c>
       <c r="AQ42" s="0">
         <v>0.95851216022889763</v>
@@ -15169,7 +15170,7 @@
         <v>1.3096519555077133</v>
       </c>
       <c r="AX42" s="0">
-        <v>1.2255646713258372</v>
+        <v>1.2255646713258373</v>
       </c>
       <c r="AY42" s="0">
         <v>1.2672733400741478</v>
@@ -15178,7 +15179,7 @@
         <v>0.48165987402741711</v>
       </c>
       <c r="BA42" s="0">
-        <v>0.80738177623990703</v>
+        <v>0.80738177623990704</v>
       </c>
       <c r="BB42" s="0">
         <v>0.22669032130889</v>
@@ -15217,7 +15218,7 @@
         <v>1.4716959267628471</v>
       </c>
       <c r="BN42" s="0">
-        <v>1.366035392735174</v>
+        <v>1.3660353927351741</v>
       </c>
       <c r="BO42" s="0">
         <v>0.72047731622199651</v>
@@ -15265,7 +15266,7 @@
         <v>1.1623547056617913</v>
       </c>
       <c r="CD42" s="0">
-        <v>1.4615384615384603</v>
+        <v>1.4615384615384604</v>
       </c>
       <c r="CE42" s="0">
         <v>1.5873015873015859</v>
@@ -15447,7 +15448,7 @@
         <v>1.4129020263989576</v>
       </c>
       <c r="V43" s="0">
-        <v>0.61274509803921517</v>
+        <v>0.61274509803921518</v>
       </c>
       <c r="W43" s="0">
         <v>1.0085470085470076</v>
@@ -15648,7 +15649,7 @@
         <v>1.1174362218005471</v>
       </c>
       <c r="CK43" s="0">
-        <v>0.94224492691925565</v>
+        <v>0.94224492691925566</v>
       </c>
       <c r="CL43" s="0">
         <v>1.0894278135657436</v>
@@ -15657,7 +15658,7 @@
         <v>0.95025153717160349</v>
       </c>
       <c r="CN43" s="0">
-        <v>0.40679588418281853</v>
+        <v>0.40679588418281854</v>
       </c>
       <c r="CO43" s="0">
         <v>0.63034470598607018</v>
@@ -15788,7 +15789,7 @@
         <v>1.1318795430944955</v>
       </c>
       <c r="O44" s="0">
-        <v>1.1535165776811009</v>
+        <v>1.153516577681101</v>
       </c>
       <c r="P44" s="0">
         <v>1.0294034010123405</v>
@@ -15815,7 +15816,7 @@
         <v>0.9914529914529906</v>
       </c>
       <c r="X44" s="0">
-        <v>0.83380708736024189</v>
+        <v>0.8338070873602419</v>
       </c>
       <c r="Y44" s="0">
         <v>0.28825995807127858</v>
@@ -15947,7 +15948,7 @@
         <v>0.64167510976021558</v>
       </c>
       <c r="BP44" s="0">
-        <v>1.2492651381540258</v>
+        <v>1.2492651381540259</v>
       </c>
       <c r="BQ44" s="0">
         <v>1.2921751615218942</v>
@@ -16231,7 +16232,7 @@
         <v>0.91385767790262096</v>
       </c>
       <c r="AP45" s="0">
-        <v>0.8682855040470927</v>
+        <v>0.86828550404709271</v>
       </c>
       <c r="AQ45" s="0">
         <v>0.90128755364806779</v>
@@ -16336,10 +16337,10 @@
         <v>0.64507081755714435</v>
       </c>
       <c r="BY45" s="0">
-        <v>0.34838350055741329</v>
+        <v>0.3483835005574133</v>
       </c>
       <c r="BZ45" s="0">
-        <v>0.73723012111637642</v>
+        <v>0.73723012111637643</v>
       </c>
       <c r="CA45" s="0">
         <v>0.55137844611528763</v>
@@ -16530,16 +16531,16 @@
         <v>1.0243802499487877</v>
       </c>
       <c r="U46" s="0">
-        <v>1.1898122327570257</v>
+        <v>1.1898122327570258</v>
       </c>
       <c r="V46" s="0">
         <v>0.50551470588235625</v>
       </c>
       <c r="W46" s="0">
-        <v>0.78632478632479152</v>
+        <v>0.78632478632479153</v>
       </c>
       <c r="X46" s="0">
-        <v>0.81485692628387862</v>
+        <v>0.81485692628387863</v>
       </c>
       <c r="Y46" s="0">
         <v>0.10482180293501117</v>
@@ -16560,7 +16561,7 @@
         <v>1.189626457292418</v>
       </c>
       <c r="AE46" s="0">
-        <v>0.81967213114754633</v>
+        <v>0.81967213114754634</v>
       </c>
       <c r="AF46" s="0">
         <v>0.28070175438596673</v>
@@ -16599,7 +16600,7 @@
         <v>0.81545064377682941</v>
       </c>
       <c r="AR46" s="0">
-        <v>0.87227414330218644</v>
+        <v>0.87227414330218645</v>
       </c>
       <c r="AS46" s="0">
         <v>0.59523809523809912</v>
@@ -16704,7 +16705,7 @@
         <v>0.53975776724592239</v>
       </c>
       <c r="CA46" s="0">
-        <v>0.6015037593985002</v>
+        <v>0.60150375939850021</v>
       </c>
       <c r="CB46" s="0">
         <v>0.83989501312336501</v>
@@ -16734,7 +16735,7 @@
         <v>0.81172253847776199</v>
       </c>
       <c r="CK46" s="0">
-        <v>0.80601674471406803</v>
+        <v>0.80601674471406804</v>
       </c>
       <c r="CL46" s="0">
         <v>0.81786030061892667</v>
@@ -16910,7 +16911,7 @@
         <v>1.0066346373827491</v>
       </c>
       <c r="AA47" s="0">
-        <v>0.23453532688361164</v>
+        <v>0.23453532688361165</v>
       </c>
       <c r="AB47" s="0">
         <v>0.40874718986306935</v>
@@ -16967,7 +16968,7 @@
         <v>0.19841269841269824</v>
       </c>
       <c r="AT47" s="0">
-        <v>1.8363939899833039</v>
+        <v>1.836393989983304</v>
       </c>
       <c r="AU47" s="0">
         <v>0.91493570722057294</v>
@@ -16985,7 +16986,7 @@
         <v>1.1998651836872252</v>
       </c>
       <c r="AZ47" s="0">
-        <v>0.28405582314437416</v>
+        <v>0.28405582314437417</v>
       </c>
       <c r="BA47" s="0">
         <v>0.31456432840515858</v>
@@ -17111,7 +17112,7 @@
         <v>0.46284051838138018</v>
       </c>
       <c r="CP47" s="0">
-        <v>0.13191030099532305</v>
+        <v>0.13191030099532306</v>
       </c>
       <c r="CQ47" s="0">
         <v>0.0054182921543129555</v>
@@ -17230,7 +17231,7 @@
         <v>0.79914757591901897</v>
       </c>
       <c r="M48" s="0">
-        <v>0.91476091476091403</v>
+        <v>0.91476091476091404</v>
       </c>
       <c r="N48" s="0">
         <v>0.76843198338525376</v>
@@ -17260,7 +17261,7 @@
         <v>0.21446078431372528</v>
       </c>
       <c r="W48" s="0">
-        <v>0.66666666666666607</v>
+        <v>0.66666666666666608</v>
       </c>
       <c r="X48" s="0">
         <v>0.66325563767291962</v>
@@ -17269,7 +17270,7 @@
         <v>0.078616352201257789</v>
       </c>
       <c r="Z48" s="0">
-        <v>0.75497597803706173</v>
+        <v>0.75497597803706174</v>
       </c>
       <c r="AA48" s="0">
         <v>0.20521841102316019</v>
@@ -17299,7 +17300,7 @@
         <v>0.54727880814837282</v>
       </c>
       <c r="AJ48" s="0">
-        <v>0.25799793601651166</v>
+        <v>0.25799793601651167</v>
       </c>
       <c r="AK48" s="0">
         <v>0.58688061808186565</v>
@@ -17350,7 +17351,7 @@
         <v>0.16055329134247237</v>
       </c>
       <c r="BA48" s="0">
-        <v>0.32504980601866384</v>
+        <v>0.32504980601866385</v>
       </c>
       <c r="BB48" s="0">
         <v>0.039424403705893916</v>
@@ -17446,7 +17447,7 @@
         <v>0.11514104778353472</v>
       </c>
       <c r="CG48" s="0">
-        <v>1.0045500206819113</v>
+        <v>1.0045500206819114</v>
       </c>
       <c r="CH48" s="0">
         <v>1.0202729561415123</v>
@@ -17562,10 +17563,10 @@
         <v>0.79444723197859102</v>
       </c>
       <c r="C49" s="0">
-        <v>0.65399911621740991</v>
+        <v>0.65399911621740992</v>
       </c>
       <c r="D49" s="0">
-        <v>0.75676857088216753</v>
+        <v>0.75676857088216754</v>
       </c>
       <c r="E49" s="0">
         <v>0.80677818272435531</v>
@@ -17652,7 +17653,7 @@
         <v>0.70175438596491169</v>
       </c>
       <c r="AG49" s="0">
-        <v>0.26407122378149966</v>
+        <v>0.26407122378149967</v>
       </c>
       <c r="AH49" s="0">
         <v>0.5946717411988578</v>
@@ -17721,7 +17722,7 @@
         <v>0.30472320975114242</v>
       </c>
       <c r="BD49" s="0">
-        <v>0.45906132237067448</v>
+        <v>0.45906132237067449</v>
       </c>
       <c r="BE49" s="0">
         <v>0.42194092827004182</v>
@@ -17733,7 +17734,7 @@
         <v>0.26494146642020922</v>
       </c>
       <c r="BH49" s="0">
-        <v>0.27331548415885742</v>
+        <v>0.27331548415885743</v>
       </c>
       <c r="BI49" s="0">
         <v>0.58812981889904914</v>
@@ -17984,7 +17985,7 @@
         <v>0.12254901960784302</v>
       </c>
       <c r="W50" s="0">
-        <v>0.66666666666666607</v>
+        <v>0.66666666666666608</v>
       </c>
       <c r="X50" s="0">
         <v>0.51165434906196661</v>
@@ -17993,7 +17994,7 @@
         <v>0.026205450733752599</v>
       </c>
       <c r="Z50" s="0">
-        <v>0.75497597803706173</v>
+        <v>0.75497597803706174</v>
       </c>
       <c r="AA50" s="0">
         <v>0.17590149516270873</v>
@@ -18014,7 +18015,7 @@
         <v>0</v>
       </c>
       <c r="AG50" s="0">
-        <v>0.26407122378149966</v>
+        <v>0.26407122378149967</v>
       </c>
       <c r="AH50" s="0">
         <v>0.55502695845226724</v>
@@ -18035,7 +18036,7 @@
         <v>0.89589125733703967</v>
       </c>
       <c r="AN50" s="0">
-        <v>0.21729682746631881</v>
+        <v>0.21729682746631882</v>
       </c>
       <c r="AO50" s="0">
         <v>0.73408239700374467</v>
@@ -18083,7 +18084,7 @@
         <v>0.21584560690705923</v>
       </c>
       <c r="BD50" s="0">
-        <v>0.3357314148681052</v>
+        <v>0.33573141486810521</v>
       </c>
       <c r="BE50" s="0">
         <v>0.39068604469448315</v>
@@ -18095,7 +18096,7 @@
         <v>0.23413431916204538</v>
       </c>
       <c r="BH50" s="0">
-        <v>0.27331548415885742</v>
+        <v>0.27331548415885743</v>
       </c>
       <c r="BI50" s="0">
         <v>0.44468352160659813</v>
@@ -18280,7 +18281,7 @@
     </row>
     <row r="51">
       <c r="A51" s="0">
-        <v>0.48705872881697015</v>
+        <v>0.48705872881697016</v>
       </c>
       <c r="B51" s="0">
         <v>0.56865696604783356</v>
@@ -18292,7 +18293,7 @@
         <v>0.67207605933939774</v>
       </c>
       <c r="E51" s="0">
-        <v>0.55758028844656204</v>
+        <v>0.55758028844656205</v>
       </c>
       <c r="F51" s="0">
         <v>0.68290723365183148</v>
@@ -18325,7 +18326,7 @@
         <v>0.42844901456726614</v>
       </c>
       <c r="P51" s="0">
-        <v>0.64835352328954043</v>
+        <v>0.64835352328954044</v>
       </c>
       <c r="Q51" s="0">
         <v>0.2057613168724278</v>
@@ -18391,7 +18392,7 @@
         <v>0.37144342916573775</v>
       </c>
       <c r="AL51" s="0">
-        <v>0.19346101760495243</v>
+        <v>0.19346101760495244</v>
       </c>
       <c r="AM51" s="0">
         <v>0.80321285140562182</v>
@@ -18448,7 +18449,7 @@
         <v>0.29462144570058213</v>
       </c>
       <c r="BE51" s="0">
-        <v>0.20315674324113125</v>
+        <v>0.20315674324113126</v>
       </c>
       <c r="BF51" s="0">
         <v>0.90240177703734481</v>
@@ -18651,7 +18652,7 @@
         <v>0.3505670938282513</v>
       </c>
       <c r="D52" s="0">
-        <v>0.59831161380214692</v>
+        <v>0.59831161380214693</v>
       </c>
       <c r="E52" s="0">
         <v>0.50151076223405866</v>
@@ -18783,7 +18784,7 @@
         <v>0.66147378832838721</v>
       </c>
       <c r="AV52" s="0">
-        <v>0.87189805499664585</v>
+        <v>0.87189805499664586</v>
       </c>
       <c r="AW52" s="0">
         <v>1.0674560459275195</v>
@@ -18885,7 +18886,7 @@
         <v>0.47494063242094697</v>
       </c>
       <c r="CD52" s="0">
-        <v>0.64102564102564052</v>
+        <v>0.64102564102564053</v>
       </c>
       <c r="CE52" s="0">
         <v>0.12698412698412687</v>
@@ -19040,7 +19041,7 @@
         <v>0.49724738057183404</v>
       </c>
       <c r="M53" s="0">
-        <v>0.44352044352044317</v>
+        <v>0.44352044352044318</v>
       </c>
       <c r="N53" s="0">
         <v>0.40498442367601212</v>
@@ -19280,7 +19281,7 @@
         <v>0.035893754486719276</v>
       </c>
       <c r="CO53" s="0">
-        <v>0.13224014810896575</v>
+        <v>0.13224014810896576</v>
       </c>
       <c r="CP53" s="0">
         <v>0.015989127393372493</v>
@@ -19411,7 +19412,7 @@
         <v>0.30321007184760368</v>
       </c>
       <c r="P54" s="0">
-        <v>0.30711482682136126</v>
+        <v>0.30711482682136127</v>
       </c>
       <c r="Q54" s="0">
         <v>0.46296296296296252</v>
@@ -19483,7 +19484,7 @@
         <v>0.80321285140562182</v>
       </c>
       <c r="AN54" s="0">
-        <v>0.21729682746631881</v>
+        <v>0.21729682746631882</v>
       </c>
       <c r="AO54" s="0">
         <v>0.49438202247190971</v>
@@ -19501,13 +19502,13 @@
         <v>0.26455026455026431</v>
       </c>
       <c r="AT54" s="0">
-        <v>0.44518642181413431</v>
+        <v>0.44518642181413432</v>
       </c>
       <c r="AU54" s="0">
         <v>0.50074183976261089</v>
       </c>
       <c r="AV54" s="0">
-        <v>0.49929204858782283</v>
+        <v>0.49929204858782284</v>
       </c>
       <c r="AW54" s="0">
         <v>0.8880516684607096</v>
@@ -19534,7 +19535,7 @@
         <v>0.14388489208633079</v>
       </c>
       <c r="BE54" s="0">
-        <v>0.20315674324113125</v>
+        <v>0.20315674324113126</v>
       </c>
       <c r="BF54" s="0">
         <v>0.74968763015410178</v>
@@ -19585,7 +19586,7 @@
         <v>0.03108486167236553</v>
       </c>
       <c r="BV54" s="0">
-        <v>0.76986076986076923</v>
+        <v>0.76986076986076924</v>
       </c>
       <c r="BW54" s="0">
         <v>0.3216374269005845</v>
@@ -19600,7 +19601,7 @@
         <v>0.10531858873091091</v>
       </c>
       <c r="CA54" s="0">
-        <v>0.25062656641603986</v>
+        <v>0.25062656641603987</v>
       </c>
       <c r="CB54" s="0">
         <v>0.31496062992125956</v>
@@ -19737,7 +19738,7 @@
         <v>0.22978347326557816</v>
       </c>
       <c r="D55" s="0">
-        <v>0.44805070622626852</v>
+        <v>0.44805070622626853</v>
       </c>
       <c r="E55" s="0">
         <v>0.35199202566738541</v>
@@ -19803,7 +19804,7 @@
         <v>0.026205450733752793</v>
       </c>
       <c r="Z55" s="0">
-        <v>0.22878059940517192</v>
+        <v>0.22878059940517193</v>
       </c>
       <c r="AA55" s="0">
         <v>0.029316915860451674</v>
@@ -19824,7 +19825,7 @@
         <v>0.14035087719298336</v>
       </c>
       <c r="AG55" s="0">
-        <v>0.090538705296514851</v>
+        <v>0.090538705296514852</v>
       </c>
       <c r="AH55" s="0">
         <v>0.30130034887409013</v>
@@ -19842,7 +19843,7 @@
         <v>0.051589604694654359</v>
       </c>
       <c r="AM55" s="0">
-        <v>0.49428483163423242</v>
+        <v>0.49428483163423243</v>
       </c>
       <c r="AN55" s="0">
         <v>0.043459365493264082</v>
@@ -19935,7 +19936,7 @@
         <v>0.46661880832735403</v>
       </c>
       <c r="BR55" s="0">
-        <v>0.4924517639460757</v>
+        <v>0.49245176394607571</v>
       </c>
       <c r="BS55" s="0">
         <v>0.0080778706732905735</v>
@@ -20129,7 +20130,7 @@
         <v>0.31878031878031854</v>
       </c>
       <c r="N56" s="0">
-        <v>0.32191069574247116</v>
+        <v>0.32191069574247117</v>
       </c>
       <c r="O56" s="0">
         <v>0.2175202689341505</v>
@@ -20207,7 +20208,7 @@
         <v>0.6178560395427859</v>
       </c>
       <c r="AN56" s="0">
-        <v>0.17383746197305502</v>
+        <v>0.17383746197305503</v>
       </c>
       <c r="AO56" s="0">
         <v>0.2546816479400747</v>
@@ -20330,7 +20331,7 @@
         <v>0.4199475065616794</v>
       </c>
       <c r="CC56" s="0">
-        <v>0.24996875390576156</v>
+        <v>0.24996875390576157</v>
       </c>
       <c r="CD56" s="0">
         <v>0.56410256410256354</v>
@@ -20509,7 +20510,7 @@
         <v>0.22754713476362942</v>
       </c>
       <c r="T57" s="0">
-        <v>0.21853445332240642</v>
+        <v>0.21853445332240643</v>
       </c>
       <c r="U57" s="0">
         <v>0.46477040342070974</v>
@@ -20563,7 +20564,7 @@
         <v>0.12629076591635083</v>
       </c>
       <c r="AL57" s="0">
-        <v>0.051589604694653977</v>
+        <v>0.051589604694653978</v>
       </c>
       <c r="AM57" s="0">
         <v>0.49428483163422882</v>
@@ -20844,7 +20845,7 @@
         <v>0.17264530980241688</v>
       </c>
       <c r="K58" s="0">
-        <v>0.17103762827822105</v>
+        <v>0.17103762827822106</v>
       </c>
       <c r="L58" s="0">
         <v>0.14207068016338115</v>
@@ -20880,7 +20881,7 @@
         <v>0.015318627450980378</v>
       </c>
       <c r="W58" s="0">
-        <v>0.085470085470085388</v>
+        <v>0.085470085470085389</v>
       </c>
       <c r="X58" s="0">
         <v>0.17055144968732219</v>
@@ -20982,7 +20983,7 @@
         <v>0.068516615279205148</v>
       </c>
       <c r="BE58" s="0">
-        <v>0.031254883575558653</v>
+        <v>0.031254883575558654</v>
       </c>
       <c r="BF58" s="0">
         <v>0.31931139802859893</v>
@@ -21021,7 +21022,7 @@
         <v>0.33500837520937993</v>
       </c>
       <c r="BR58" s="0">
-        <v>0.28255429078872984</v>
+        <v>0.28255429078872985</v>
       </c>
       <c r="BS58" s="0">
         <v>0.0080778706732905128</v>
@@ -21383,7 +21384,7 @@
         <v>0.3110792055515671</v>
       </c>
       <c r="BR59" s="0">
-        <v>0.23411641236780475</v>
+        <v>0.23411641236780476</v>
       </c>
       <c r="BS59" s="0">
         <v>0</v>
@@ -21407,7 +21408,7 @@
         <v>0.027870680044593064</v>
       </c>
       <c r="BZ59" s="0">
-        <v>0.026329647182727726</v>
+        <v>0.026329647182727727</v>
       </c>
       <c r="CA59" s="0">
         <v>0</v>
@@ -21580,7 +21581,7 @@
         <v>0.07268951194184832</v>
       </c>
       <c r="O60" s="0">
-        <v>0.098872849515522956</v>
+        <v>0.098872849515522957</v>
       </c>
       <c r="P60" s="0">
         <v>0.1251208553716657</v>
@@ -21760,7 +21761,7 @@
         <v>0.42588042588042552</v>
       </c>
       <c r="BW60" s="0">
-        <v>0.04385964912280698</v>
+        <v>0.043859649122806981</v>
       </c>
       <c r="BX60" s="0">
         <v>0.04206983592763984</v>
@@ -22044,7 +22045,7 @@
         <v>0.17139876294805859</v>
       </c>
       <c r="AW61" s="0">
-        <v>0.50233225690706806</v>
+        <v>0.50233225690706807</v>
       </c>
       <c r="AX61" s="0">
         <v>0.070900435531246767</v>
@@ -22131,13 +22132,13 @@
         <v>0.013935340022296532</v>
       </c>
       <c r="BZ61" s="0">
-        <v>0.026329647182727726</v>
+        <v>0.026329647182727727</v>
       </c>
       <c r="CA61" s="0">
         <v>0</v>
       </c>
       <c r="CB61" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC61" s="0">
         <v>0.1124859392575927</v>
@@ -22167,7 +22168,7 @@
         <v>0.068114091102596794</v>
       </c>
       <c r="CL61" s="0">
-        <v>0.047366426676771461</v>
+        <v>0.047366426676771462</v>
       </c>
       <c r="CM61" s="0">
         <v>0.03726476616359229</v>
@@ -22382,7 +22383,7 @@
         <v>0.086918730986527512</v>
       </c>
       <c r="AO62" s="0">
-        <v>0.089887640449438116</v>
+        <v>0.089887640449438117</v>
       </c>
       <c r="AP62" s="0">
         <v>0.014716703458425299</v>
@@ -22427,7 +22428,7 @@
         <v>0.012696800406297603</v>
       </c>
       <c r="BD62" s="0">
-        <v>0.020554984583761544</v>
+        <v>0.020554984583761545</v>
       </c>
       <c r="BE62" s="0">
         <v>0.015627441787779327</v>
@@ -22475,7 +22476,7 @@
         <v>0.0040389353366452564</v>
       </c>
       <c r="BT62" s="0">
-        <v>0.016959213092512491</v>
+        <v>0.016959213092512492</v>
       </c>
       <c r="BU62" s="0">
         <v>0.010361620557455176</v>
@@ -22493,7 +22494,7 @@
         <v>0</v>
       </c>
       <c r="BZ62" s="0">
-        <v>0.026329647182727726</v>
+        <v>0.026329647182727727</v>
       </c>
       <c r="CA62" s="0">
         <v>0.050125313283207976</v>
@@ -22666,7 +22667,7 @@
         <v>0.041536863966770782</v>
       </c>
       <c r="O63" s="0">
-        <v>0.079098279612418942</v>
+        <v>0.079098279612418943</v>
       </c>
       <c r="P63" s="0">
         <v>0.096684297332651478</v>
@@ -22681,7 +22682,7 @@
         <v>0.078944924305749564</v>
       </c>
       <c r="T63" s="0">
-        <v>0.081950419995903009</v>
+        <v>0.08195041999590301</v>
       </c>
       <c r="U63" s="0">
         <v>0.13013571295779969</v>
@@ -22693,7 +22694,7 @@
         <v>0.051282051282051613</v>
       </c>
       <c r="X63" s="0">
-        <v>0.075800644305477088</v>
+        <v>0.075800644305477089</v>
       </c>
       <c r="Y63" s="0">
         <v>0</v>
@@ -22708,7 +22709,7 @@
         <v>0.040874718986307235</v>
       </c>
       <c r="AC63" s="0">
-        <v>0.44917257683215422</v>
+        <v>0.44917257683215423</v>
       </c>
       <c r="AD63" s="0">
         <v>0.35688793718772538</v>
@@ -22723,7 +22724,7 @@
         <v>0.0075448921080429037</v>
       </c>
       <c r="AH63" s="0">
-        <v>0.039644782746590806</v>
+        <v>0.039644782746590807</v>
       </c>
       <c r="AI63" s="0">
         <v>0.030404378230465386</v>
@@ -22795,7 +22796,7 @@
         <v>0</v>
       </c>
       <c r="BF63" s="0">
-        <v>0.15271414688324408</v>
+        <v>0.15271414688324409</v>
       </c>
       <c r="BG63" s="0">
         <v>0</v>
@@ -22825,7 +22826,7 @@
         <v>0.011257458065968779</v>
       </c>
       <c r="BP63" s="0">
-        <v>0.058788947677836947</v>
+        <v>0.058788947677836948</v>
       </c>
       <c r="BQ63" s="0">
         <v>0.09571667863125212</v>
@@ -22876,7 +22877,7 @@
         <v>0</v>
       </c>
       <c r="CG63" s="0">
-        <v>0.076818530993323197</v>
+        <v>0.076818530993323198</v>
       </c>
       <c r="CH63" s="0">
         <v>0.12366944922927514</v>
@@ -22998,7 +22999,7 @@
         <v>0.090156544545528974</v>
       </c>
       <c r="E64" s="0">
-        <v>0.065414447247920698</v>
+        <v>0.065414447247920699</v>
       </c>
       <c r="F64" s="0">
         <v>0.065995236865513132</v>
@@ -23022,7 +23023,7 @@
         <v>0.071035340081690573</v>
       </c>
       <c r="M64" s="0">
-        <v>0.027720027720027698</v>
+        <v>0.027720027720027699</v>
       </c>
       <c r="N64" s="0">
         <v>0.010384215991692619</v>
@@ -23151,7 +23152,7 @@
         <v>0.0084645336041984012</v>
       </c>
       <c r="BD64" s="0">
-        <v>0.020554984583761544</v>
+        <v>0.020554984583761545</v>
       </c>
       <c r="BE64" s="0">
         <v>0</v>
@@ -23199,7 +23200,7 @@
         <v>0</v>
       </c>
       <c r="BT64" s="0">
-        <v>0.0084796065462562457</v>
+        <v>0.0084796065462562458</v>
       </c>
       <c r="BU64" s="0">
         <v>0</v>
@@ -23208,7 +23209,7 @@
         <v>0.26208026208026186</v>
       </c>
       <c r="BW64" s="0">
-        <v>0.04385964912280698</v>
+        <v>0.043859649122806981</v>
       </c>
       <c r="BX64" s="0">
         <v>0.02804655728509323</v>
@@ -23223,7 +23224,7 @@
         <v>0</v>
       </c>
       <c r="CB64" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC64" s="0">
         <v>0.012498437695288078</v>
@@ -23244,7 +23245,7 @@
         <v>0.070668256702442409</v>
       </c>
       <c r="CI64" s="0">
-        <v>0.044370493621741502</v>
+        <v>0.044370493621741503</v>
       </c>
       <c r="CJ64" s="0">
         <v>0.052709255745308825</v>
@@ -23561,7 +23562,7 @@
         <v>0</v>
       </c>
       <c r="BT65" s="0">
-        <v>0.0084796065462562457</v>
+        <v>0.0084796065462562458</v>
       </c>
       <c r="BU65" s="0">
         <v>0</v>
@@ -23570,7 +23571,7 @@
         <v>0.049140049140049095</v>
       </c>
       <c r="BW65" s="0">
-        <v>0.04385964912280698</v>
+        <v>0.043859649122806981</v>
       </c>
       <c r="BX65" s="0">
         <v>0</v>
@@ -23585,7 +23586,7 @@
         <v>0.050125313283207976</v>
       </c>
       <c r="CB65" s="0">
-        <v>0.052493438320209924</v>
+        <v>0.052493438320209925</v>
       </c>
       <c r="CC65" s="0">
         <v>0.012498437695288078</v>
@@ -23609,7 +23610,7 @@
         <v>0.055463117027176878</v>
       </c>
       <c r="CJ65" s="0">
-        <v>0.031625553447185296</v>
+        <v>0.031625553447185297</v>
       </c>
       <c r="CK65" s="0">
         <v>0.028380871292748664</v>
@@ -23731,13 +23732,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="0">
-        <v>0.050459178524573572</v>
+        <v>0.050459178524573573</v>
       </c>
       <c r="I66" s="0">
         <v>0.060908084163898063</v>
       </c>
       <c r="J66" s="0">
-        <v>0.070336978067651323</v>
+        <v>0.070336978067651324</v>
       </c>
       <c r="K66" s="0">
         <v>0.057012542759407023</v>
@@ -23905,7 +23906,7 @@
         <v>0.10429341213280019</v>
       </c>
       <c r="BN66" s="0">
-        <v>0.031046258925799416</v>
+        <v>0.031046258925799417</v>
       </c>
       <c r="BO66" s="0">
         <v>0</v>
@@ -23932,7 +23933,7 @@
         <v>0.11466011466011455</v>
       </c>
       <c r="BW66" s="0">
-        <v>0.04385964912280698</v>
+        <v>0.043859649122806981</v>
       </c>
       <c r="BX66" s="0">
         <v>0</v>
@@ -23974,7 +23975,7 @@
         <v>0.073792958043432361</v>
       </c>
       <c r="CK66" s="0">
-        <v>0.017028522775649198</v>
+        <v>0.017028522775649199</v>
       </c>
       <c r="CL66" s="0">
         <v>0.012631047113805723</v>
@@ -24243,7 +24244,7 @@
         <v>0</v>
       </c>
       <c r="BF67" s="0">
-        <v>0.055532417048452395</v>
+        <v>0.055532417048452396</v>
       </c>
       <c r="BG67" s="0">
         <v>0</v>
@@ -24315,7 +24316,7 @@
         <v>0.02499687539057634</v>
       </c>
       <c r="CD67" s="0">
-        <v>0.038461538461538713</v>
+        <v>0.038461538461538714</v>
       </c>
       <c r="CE67" s="0">
         <v>0</v>
@@ -24500,7 +24501,7 @@
         <v>0.015318627450980265</v>
       </c>
       <c r="W68" s="0">
-        <v>0.017094017094016953</v>
+        <v>0.017094017094016954</v>
       </c>
       <c r="X68" s="0">
         <v>0.018950161076368991</v>
@@ -24686,7 +24687,7 @@
         <v>0</v>
       </c>
       <c r="CG68" s="0">
-        <v>0.017727353306151244</v>
+        <v>0.017727353306151245</v>
       </c>
       <c r="CH68" s="0">
         <v>0.01766706417561047</v>
@@ -24841,7 +24842,7 @@
         <v>0.019774569903104736</v>
       </c>
       <c r="P69" s="0">
-        <v>0.0056873116078030288</v>
+        <v>0.0056873116078030289</v>
       </c>
       <c r="Q69" s="0">
         <v>0</v>
@@ -24883,7 +24884,7 @@
         <v>0.094562647754137738</v>
       </c>
       <c r="AD69" s="0">
-        <v>0.023792529145848357</v>
+        <v>0.023792529145848358</v>
       </c>
       <c r="AE69" s="0">
         <v>0.068306010928962199</v>
@@ -25060,7 +25061,7 @@
         <v>0</v>
       </c>
       <c r="CK69" s="0">
-        <v>0.0056761742585497744</v>
+        <v>0.0056761742585497745</v>
       </c>
       <c r="CL69" s="0">
         <v>0.0063155235569029083</v>
@@ -25167,13 +25168,13 @@
         <v>0.014729709824716332</v>
       </c>
       <c r="D70" s="0">
-        <v>0.0300521815151761</v>
+        <v>0.030052181515176101</v>
       </c>
       <c r="E70" s="0">
         <v>0.012459894713889565</v>
       </c>
       <c r="F70" s="0">
-        <v>0.0086080743737625177</v>
+        <v>0.0086080743737625178</v>
       </c>
       <c r="G70" s="0">
         <v>0</v>
@@ -25344,7 +25345,7 @@
         <v>0.0036852773171180829</v>
       </c>
       <c r="BK70" s="0">
-        <v>0.034343018064427216</v>
+        <v>0.034343018064427217</v>
       </c>
       <c r="BL70" s="0">
         <v>0</v>
@@ -25565,7 +25566,7 @@
         <v>0</v>
       </c>
       <c r="P71" s="0">
-        <v>0.0056873116078030288</v>
+        <v>0.0056873116078030289</v>
       </c>
       <c r="Q71" s="0">
         <v>0</v>
@@ -25655,7 +25656,7 @@
         <v>0</v>
       </c>
       <c r="AT71" s="0">
-        <v>0.22259321090706879</v>
+        <v>0.2225932109070688</v>
       </c>
       <c r="AU71" s="0">
         <v>0.0061819980217606733</v>
@@ -25948,7 +25949,7 @@
         <v>0</v>
       </c>
       <c r="W72" s="0">
-        <v>0.017094017094016953</v>
+        <v>0.017094017094016954</v>
       </c>
       <c r="X72" s="0">
         <v>0</v>
@@ -26083,7 +26084,7 @@
         <v>0</v>
       </c>
       <c r="BP72" s="0">
-        <v>0.022045855379188527</v>
+        <v>0.022045855379188528</v>
       </c>
       <c r="BQ72" s="0">
         <v>0</v>
@@ -26134,7 +26135,7 @@
         <v>0</v>
       </c>
       <c r="CG72" s="0">
-        <v>0.017727353306151244</v>
+        <v>0.017727353306151245</v>
       </c>
       <c r="CH72" s="0">
         <v>0.013250298131707854</v>
@@ -26621,7 +26622,7 @@
         <v>0.0031149736784723912</v>
       </c>
       <c r="F74" s="0">
-        <v>0.0086080743737625177</v>
+        <v>0.0086080743737625178</v>
       </c>
       <c r="G74" s="0">
         <v>0</v>
@@ -26807,7 +26808,7 @@
         <v>0</v>
       </c>
       <c r="BP74" s="0">
-        <v>0.022045855379188527</v>
+        <v>0.022045855379188528</v>
       </c>
       <c r="BQ74" s="0">
         <v>0</v>
@@ -26861,7 +26862,7 @@
         <v>0</v>
       </c>
       <c r="CH74" s="0">
-        <v>0.0088335320878052351</v>
+        <v>0.0088335320878052352</v>
       </c>
       <c r="CI74" s="0">
         <v>0</v>
@@ -28449,7 +28450,7 @@
         <v>0</v>
       </c>
       <c r="L79" s="0">
-        <v>0.017758835020422511</v>
+        <v>0.017758835020422512</v>
       </c>
       <c r="M79" s="0">
         <v>0</v>
@@ -30675,7 +30676,7 @@
         <v>0</v>
       </c>
       <c r="AD85" s="0">
-        <v>0.023792529145848357</v>
+        <v>0.023792529145848358</v>
       </c>
       <c r="AE85" s="0">
         <v>0</v>
